--- a/datasets/day1_excel_foundations/homework/d1_homework_answers.xlsx
+++ b/datasets/day1_excel_foundations/homework/d1_homework_answers.xlsx
@@ -596,7 +596,7 @@
     <col width="22.5" customWidth="1" min="5" max="5"/>
     <col width="12.5" customWidth="1" min="6" max="6"/>
     <col width="10.5" customWidth="1" min="7" max="7"/>
-    <col width="9.5" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
     <col width="42" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -680,7 +680,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>174</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2">
         <f>IF(H2&gt;=1000,"Large",IF(H2&gt;=300,"Medium","Small"))</f>
@@ -720,7 +720,7 @@
         <v>3</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>396</v>
+        <v>240</v>
       </c>
       <c r="I3" s="2">
         <f>IF(H3&gt;=1000,"Large",IF(H3&gt;=300,"Medium","Small"))</f>
@@ -760,7 +760,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1799</v>
+        <v>1200</v>
       </c>
       <c r="I4" s="2">
         <f>IF(H4&gt;=1000,"Large",IF(H4&gt;=300,"Medium","Small"))</f>
@@ -800,7 +800,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1259</v>
+        <v>1400</v>
       </c>
       <c r="I5" s="2">
         <f>IF(H5&gt;=1000,"Large",IF(H5&gt;=300,"Medium","Small"))</f>
@@ -840,7 +840,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>146</v>
+        <v>50</v>
       </c>
       <c r="I6" s="2">
         <f>IF(H6&gt;=1000,"Large",IF(H6&gt;=300,"Medium","Small"))</f>
@@ -880,7 +880,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>3980</v>
+        <v>2800</v>
       </c>
       <c r="I7" s="2">
         <f>IF(H7&gt;=1000,"Large",IF(H7&gt;=300,"Medium","Small"))</f>
@@ -920,7 +920,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>1003</v>
+        <v>1500</v>
       </c>
       <c r="I8" s="2">
         <f>IF(H8&gt;=1000,"Large",IF(H8&gt;=300,"Medium","Small"))</f>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>794</v>
+        <v>900</v>
       </c>
       <c r="I9" s="2">
         <f>IF(H9&gt;=1000,"Large",IF(H9&gt;=300,"Medium","Small"))</f>
@@ -1000,7 +1000,7 @@
         <v>4</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>6777.6</v>
+        <v>6000</v>
       </c>
       <c r="I10" s="2">
         <f>IF(H10&gt;=1000,"Large",IF(H10&gt;=300,"Medium","Small"))</f>
@@ -1040,7 +1040,7 @@
         <v>3</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>2898</v>
+        <v>1800</v>
       </c>
       <c r="I11" s="2">
         <f>IF(H11&gt;=1000,"Large",IF(H11&gt;=300,"Medium","Small"))</f>
@@ -1080,7 +1080,7 @@
         <v>2</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>214</v>
+        <v>160</v>
       </c>
       <c r="I12" s="2">
         <f>IF(H12&gt;=1000,"Large",IF(H12&gt;=300,"Medium","Small"))</f>
@@ -1120,7 +1120,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>165.3</v>
+        <v>120</v>
       </c>
       <c r="I13" s="2">
         <f>IF(H13&gt;=1000,"Large",IF(H13&gt;=300,"Medium","Small"))</f>
@@ -1160,7 +1160,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="I14" s="2">
         <f>IF(H14&gt;=1000,"Large",IF(H14&gt;=300,"Medium","Small"))</f>
@@ -1200,7 +1200,7 @@
         <v>2</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>2759.4</v>
+        <v>2400</v>
       </c>
       <c r="I15" s="2">
         <f>IF(H15&gt;=1000,"Large",IF(H15&gt;=300,"Medium","Small"))</f>
@@ -1240,7 +1240,7 @@
         <v>3</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>1050</v>
+        <v>1500</v>
       </c>
       <c r="I16" s="2">
         <f>IF(H16&gt;=1000,"Large",IF(H16&gt;=300,"Medium","Small"))</f>
@@ -1280,7 +1280,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="I17" s="2">
         <f>IF(H17&gt;=1000,"Large",IF(H17&gt;=300,"Medium","Small"))</f>
@@ -1320,7 +1320,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>1928</v>
+        <v>1200</v>
       </c>
       <c r="I18" s="2">
         <f>IF(H18&gt;=1000,"Large",IF(H18&gt;=300,"Medium","Small"))</f>
@@ -1360,7 +1360,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>765</v>
+        <v>700</v>
       </c>
       <c r="I19" s="2">
         <f>IF(H19&gt;=1000,"Large",IF(H19&gt;=300,"Medium","Small"))</f>
@@ -1400,7 +1400,7 @@
         <v>2</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>212</v>
+        <v>100</v>
       </c>
       <c r="I20" s="2">
         <f>IF(H20&gt;=1000,"Large",IF(H20&gt;=300,"Medium","Small"))</f>
@@ -1440,7 +1440,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>1581</v>
+        <v>1400</v>
       </c>
       <c r="I21" s="2">
         <f>IF(H21&gt;=1000,"Large",IF(H21&gt;=300,"Medium","Small"))</f>
@@ -1480,7 +1480,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>1433</v>
+        <v>1500</v>
       </c>
       <c r="I22" s="2">
         <f>IF(H22&gt;=1000,"Large",IF(H22&gt;=300,"Medium","Small"))</f>
@@ -1520,7 +1520,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>1737</v>
+        <v>1500</v>
       </c>
       <c r="I23" s="2">
         <f>IF(H23&gt;=1000,"Large",IF(H23&gt;=300,"Medium","Small"))</f>
@@ -1560,7 +1560,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>812</v>
+        <v>700</v>
       </c>
       <c r="I24" s="2">
         <f>IF(H24&gt;=1000,"Large",IF(H24&gt;=300,"Medium","Small"))</f>
@@ -1600,7 +1600,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>1244</v>
+        <v>900</v>
       </c>
       <c r="I25" s="2">
         <f>IF(H25&gt;=1000,"Large",IF(H25&gt;=300,"Medium","Small"))</f>
@@ -1640,7 +1640,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>312</v>
+        <v>150</v>
       </c>
       <c r="I26" s="2">
         <f>IF(H26&gt;=1000,"Large",IF(H26&gt;=300,"Medium","Small"))</f>
@@ -1680,7 +1680,7 @@
         <v>2</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>2561.4</v>
+        <v>3000</v>
       </c>
       <c r="I27" s="2">
         <f>IF(H27&gt;=1000,"Large",IF(H27&gt;=300,"Medium","Small"))</f>
@@ -1720,7 +1720,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>645</v>
+        <v>500</v>
       </c>
       <c r="I28" s="2">
         <f>IF(H28&gt;=1000,"Large",IF(H28&gt;=300,"Medium","Small"))</f>
@@ -1760,7 +1760,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>548.25</v>
+        <v>1000</v>
       </c>
       <c r="I29" s="2">
         <f>IF(H29&gt;=1000,"Large",IF(H29&gt;=300,"Medium","Small"))</f>
@@ -1800,7 +1800,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>43.2</v>
+        <v>80</v>
       </c>
       <c r="I30" s="2">
         <f>IF(H30&gt;=1000,"Large",IF(H30&gt;=300,"Medium","Small"))</f>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>677</v>
+        <v>600</v>
       </c>
       <c r="I31" s="2">
         <f>IF(H31&gt;=1000,"Large",IF(H31&gt;=300,"Medium","Small"))</f>
@@ -1880,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>1996</v>
+        <v>1500</v>
       </c>
       <c r="I32" s="2">
         <f>IF(H32&gt;=1000,"Large",IF(H32&gt;=300,"Medium","Small"))</f>
@@ -1920,7 +1920,7 @@
         <v>1</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>1608.35</v>
+        <v>1400</v>
       </c>
       <c r="I33" s="2">
         <f>IF(H33&gt;=1000,"Large",IF(H33&gt;=300,"Medium","Small"))</f>
@@ -1960,7 +1960,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>848</v>
+        <v>800</v>
       </c>
       <c r="I34" s="2">
         <f>IF(H34&gt;=1000,"Large",IF(H34&gt;=300,"Medium","Small"))</f>
@@ -2000,7 +2000,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>94.5</v>
+        <v>100</v>
       </c>
       <c r="I35" s="2">
         <f>IF(H35&gt;=1000,"Large",IF(H35&gt;=300,"Medium","Small"))</f>
@@ -2040,7 +2040,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="I36" s="2">
         <f>IF(H36&gt;=1000,"Large",IF(H36&gt;=300,"Medium","Small"))</f>

--- a/datasets/day1_excel_foundations/homework/d1_homework_answers.xlsx
+++ b/datasets/day1_excel_foundations/homework/d1_homework_answers.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Answers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Branch Orders'!$A$1:$I$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Branch Orders'!$A$1:$I$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,14 +586,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
     <col width="19.5" customWidth="1" min="3" max="3"/>
     <col width="14.5" customWidth="1" min="4" max="4"/>
-    <col width="22.5" customWidth="1" min="5" max="5"/>
+    <col width="20.5" customWidth="1" min="5" max="5"/>
     <col width="12.5" customWidth="1" min="6" max="6"/>
     <col width="10.5" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
@@ -650,15 +650,15 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>O0046</t>
+          <t>B001</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>45571</v>
+        <v>46058</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -668,19 +668,19 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>iPhone 16</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Smart Home</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="G2" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="I2" s="2">
         <f>IF(H2&gt;=1000,"Large",IF(H2&gt;=300,"Medium","Small"))</f>
@@ -690,37 +690,37 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>O0047</t>
+          <t>B002</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>45489</v>
+        <v>46093</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Amara Otieno</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>USB-C Hub 7in1</t>
+          <t>Dell XPS 15</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Accessory</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>240</v>
+        <v>3000</v>
       </c>
       <c r="I3" s="2">
         <f>IF(H3&gt;=1000,"Large",IF(H3&gt;=300,"Medium","Small"))</f>
@@ -730,15 +730,15 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>O0048</t>
+          <t>B003</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>45478</v>
+        <v>45981</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Farai Ncube</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -748,19 +748,19 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>HP Spectre x360</t>
+          <t>Echo Dot 6</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="G4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>1200</v>
+        <v>100</v>
       </c>
       <c r="I4" s="2">
         <f>IF(H4&gt;=1000,"Large",IF(H4&gt;=300,"Medium","Small"))</f>
@@ -770,37 +770,37 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>O0049</t>
+          <t>B004</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>45951</v>
+        <v>46040</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Tendai Moyo</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="I5" s="2">
         <f>IF(H5&gt;=1000,"Large",IF(H5&gt;=300,"Medium","Small"))</f>
@@ -810,11 +810,11 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>O0050</t>
+          <t>B005</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>45438</v>
+        <v>45903</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Laptop Sleeve 15in</t>
+          <t>Wireless Mouse Pro</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="I6" s="2">
         <f>IF(H6&gt;=1000,"Large",IF(H6&gt;=300,"Medium","Small"))</f>
@@ -850,37 +850,37 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>O0051</t>
+          <t>B006</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>45764</v>
+        <v>46139</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Simbarashe Mutasa</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>iPad Air 6</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>2800</v>
+        <v>800</v>
       </c>
       <c r="I7" s="2">
         <f>IF(H7&gt;=1000,"Large",IF(H7&gt;=300,"Medium","Small"))</f>
@@ -890,25 +890,25 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>O0052</t>
+          <t>B007</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>45554</v>
+        <v>46187</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Dell XPS 15</t>
+          <t>ThinkPad X1</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="I8" s="2">
         <f>IF(H8&gt;=1000,"Large",IF(H8&gt;=300,"Medium","Small"))</f>
@@ -930,11 +930,11 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>O0053</t>
+          <t>B008</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>46172</v>
+        <v>46000</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -948,19 +948,19 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Pixel 9 Pro</t>
+          <t>Surface Go 4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="I9" s="2">
         <f>IF(H9&gt;=1000,"Large",IF(H9&gt;=300,"Medium","Small"))</f>
@@ -970,37 +970,37 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>O0054</t>
+          <t>B009</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>46352</v>
+        <v>46164</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Amara Otieno</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Dell XPS 15</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>6000</v>
+        <v>200</v>
       </c>
       <c r="I10" s="2">
         <f>IF(H10&gt;=1000,"Large",IF(H10&gt;=300,"Medium","Small"))</f>
@@ -1010,37 +1010,37 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>O0055</t>
+          <t>B010</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>46306</v>
+        <v>46204</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Amara Otieno</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>HP Spectre x360</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="I11" s="2">
         <f>IF(H11&gt;=1000,"Large",IF(H11&gt;=300,"Medium","Small"))</f>
@@ -1050,20 +1050,20 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>O0056</t>
+          <t>B011</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>45919</v>
+        <v>45946</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Rutendo Chikafu</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="I12" s="2">
         <f>IF(H12&gt;=1000,"Large",IF(H12&gt;=300,"Medium","Small"))</f>
@@ -1090,15 +1090,15 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>O0057</t>
+          <t>B012</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>45444</v>
+        <v>46081</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Farai Ncube</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1108,948 +1108,28 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Bluetooth Headphones</t>
+          <t>Pixel 9 Pro</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Accessory</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="G13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="I13" s="2">
         <f>IF(H13&gt;=1000,"Large",IF(H13&gt;=300,"Medium","Small"))</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>O0058</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>46169</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Rutendo Chikafu</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Laptop Sleeve 15in</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Accessory</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="I14" s="2">
-        <f>IF(H14&gt;=1000,"Large",IF(H14&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>O0059</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>46113</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Farai Ncube</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>HP Spectre x360</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>2400</v>
-      </c>
-      <c r="I15" s="2">
-        <f>IF(H15&gt;=1000,"Large",IF(H15&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>O0060</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>46248</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Nyasha Banda</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Galaxy Tab S10</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I16" s="2">
-        <f>IF(H16&gt;=1000,"Large",IF(H16&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>O0061</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>45452</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Tendai Moyo</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>iPhone 16</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I17" s="2">
-        <f>IF(H17&gt;=1000,"Large",IF(H17&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>O0062</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>45979</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>HP Spectre x360</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I18" s="2">
-        <f>IF(H18&gt;=1000,"Large",IF(H18&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>O0063</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>45761</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Simbarashe Mutasa</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>iPad Air 6</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="I19" s="2">
-        <f>IF(H19&gt;=1000,"Large",IF(H19&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>O0064</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>45521</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Laptop Sleeve 15in</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Accessory</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="I20" s="2">
-        <f>IF(H20&gt;=1000,"Large",IF(H20&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>O0065</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>46170</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>ThinkPad X1</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>1400</v>
-      </c>
-      <c r="I21" s="2">
-        <f>IF(H21&gt;=1000,"Large",IF(H21&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>O0066</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>45744</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Dell XPS 15</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I22" s="2">
-        <f>IF(H22&gt;=1000,"Large",IF(H22&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>O0067</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>46107</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Rutendo Chikafu</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Dell XPS 15</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I23" s="2">
-        <f>IF(H23&gt;=1000,"Large",IF(H23&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>O0068</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>45809</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Farai Ncube</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>iPad Air 6</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="I24" s="2">
-        <f>IF(H24&gt;=1000,"Large",IF(H24&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>O0069</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>46352</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Thabo Nkosi</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Pixel 9 Pro</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>900</v>
-      </c>
-      <c r="I25" s="2">
-        <f>IF(H25&gt;=1000,"Large",IF(H25&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>O0070</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>45788</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Nyasha Banda</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="I26" s="2">
-        <f>IF(H26&gt;=1000,"Large",IF(H26&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>O0071</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>46284</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Kudzai Sibanda</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Dell XPS 15</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I27" s="2">
-        <f>IF(H27&gt;=1000,"Large",IF(H27&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>O0072</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>45544</v>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Galaxy Tab S10</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="I28" s="2">
-        <f>IF(H28&gt;=1000,"Large",IF(H28&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>O0073</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>45419</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Chipo Marufu</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>iPhone 16</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I29" s="2">
-        <f>IF(H29&gt;=1000,"Large",IF(H29&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>O0074</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>45977</v>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Rutendo Chikafu</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>USB-C Hub 7in1</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Accessory</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="I30" s="2">
-        <f>IF(H30&gt;=1000,"Large",IF(H30&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>O0075</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>46145</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Kagiso Molefe</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Botswana</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>OnePlus 13</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>600</v>
-      </c>
-      <c r="I31" s="2">
-        <f>IF(H31&gt;=1000,"Large",IF(H31&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>O0076</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>45446</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Simbarashe Mutasa</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Dell XPS 15</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I32" s="2">
-        <f>IF(H32&gt;=1000,"Large",IF(H32&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>O0077</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>45537</v>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Kudzai Sibanda</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>ThinkPad X1</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>1400</v>
-      </c>
-      <c r="I33" s="2">
-        <f>IF(H33&gt;=1000,"Large",IF(H33&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>O0078</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>46050</v>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Thabo Nkosi</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Galaxy S24</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>800</v>
-      </c>
-      <c r="I34" s="2">
-        <f>IF(H34&gt;=1000,"Large",IF(H34&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>O0079</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>45612</v>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Chipo Marufu</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Echo Dot 6</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="I35" s="2">
-        <f>IF(H35&gt;=1000,"Large",IF(H35&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>O0080</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>45691</v>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Thabo Nkosi</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Wireless Mouse Pro</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Accessory</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="I36" s="2">
-        <f>IF(H36&gt;=1000,"Large",IF(H36&gt;=300,"Medium","Small"))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I36"/>
-  <conditionalFormatting sqref="H2:H36">
+  <autoFilter ref="A1:I13"/>
+  <conditionalFormatting sqref="H2:H13">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -2098,7 +1178,7 @@
         </is>
       </c>
       <c r="B4" s="5">
-        <f>SUM('Branch Orders'!H2:H36)</f>
+        <f>SUM('Branch Orders'!H2:H13)</f>
         <v/>
       </c>
     </row>
@@ -2109,7 +1189,7 @@
         </is>
       </c>
       <c r="B5" s="9">
-        <f>COUNT('Branch Orders'!H2:H36)</f>
+        <f>COUNT('Branch Orders'!H2:H13)</f>
         <v/>
       </c>
     </row>
@@ -2120,7 +1200,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>AVERAGE('Branch Orders'!H2:H36)</f>
+        <f>AVERAGE('Branch Orders'!H2:H13)</f>
         <v/>
       </c>
     </row>
@@ -2131,7 +1211,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>MAX('Branch Orders'!H2:H36)</f>
+        <f>MAX('Branch Orders'!H2:H13)</f>
         <v/>
       </c>
     </row>
@@ -2149,7 +1229,7 @@
         </is>
       </c>
       <c r="B9" s="9">
-        <f>COUNTIF('Branch Orders'!H2:H36,"&gt;1000")</f>
+        <f>COUNTIF('Branch Orders'!H2:H13,"&gt;1000")</f>
         <v/>
       </c>
     </row>
@@ -2160,7 +1240,7 @@
         </is>
       </c>
       <c r="B10" s="5">
-        <f>SUMIF('Branch Orders'!D2:D36,"&lt;&gt;Zimbabwe",'Branch Orders'!H2:H36)</f>
+        <f>SUMIF('Branch Orders'!D2:D13,"&lt;&gt;Zimbabwe",'Branch Orders'!H2:H13)</f>
         <v/>
       </c>
     </row>
@@ -2196,11 +1276,11 @@
         </is>
       </c>
       <c r="B14" s="11">
-        <f>SUMIF('Branch Orders'!F2:F36,A14,'Branch Orders'!H2:H36)</f>
+        <f>SUMIF('Branch Orders'!F2:F13,A14,'Branch Orders'!H2:H13)</f>
         <v/>
       </c>
       <c r="C14" s="12">
-        <f>COUNTIF('Branch Orders'!F2:F36,A14)</f>
+        <f>COUNTIF('Branch Orders'!F2:F13,A14)</f>
         <v/>
       </c>
     </row>
@@ -2211,11 +1291,11 @@
         </is>
       </c>
       <c r="B15" s="11">
-        <f>SUMIF('Branch Orders'!F2:F36,A15,'Branch Orders'!H2:H36)</f>
+        <f>SUMIF('Branch Orders'!F2:F13,A15,'Branch Orders'!H2:H13)</f>
         <v/>
       </c>
       <c r="C15" s="12">
-        <f>COUNTIF('Branch Orders'!F2:F36,A15)</f>
+        <f>COUNTIF('Branch Orders'!F2:F13,A15)</f>
         <v/>
       </c>
     </row>
@@ -2226,11 +1306,11 @@
         </is>
       </c>
       <c r="B16" s="11">
-        <f>SUMIF('Branch Orders'!F2:F36,A16,'Branch Orders'!H2:H36)</f>
+        <f>SUMIF('Branch Orders'!F2:F13,A16,'Branch Orders'!H2:H13)</f>
         <v/>
       </c>
       <c r="C16" s="12">
-        <f>COUNTIF('Branch Orders'!F2:F36,A16)</f>
+        <f>COUNTIF('Branch Orders'!F2:F13,A16)</f>
         <v/>
       </c>
     </row>
@@ -2241,11 +1321,11 @@
         </is>
       </c>
       <c r="B17" s="11">
-        <f>SUMIF('Branch Orders'!F2:F36,A17,'Branch Orders'!H2:H36)</f>
+        <f>SUMIF('Branch Orders'!F2:F13,A17,'Branch Orders'!H2:H13)</f>
         <v/>
       </c>
       <c r="C17" s="12">
-        <f>COUNTIF('Branch Orders'!F2:F36,A17)</f>
+        <f>COUNTIF('Branch Orders'!F2:F13,A17)</f>
         <v/>
       </c>
     </row>
@@ -2256,11 +1336,11 @@
         </is>
       </c>
       <c r="B18" s="11">
-        <f>SUMIF('Branch Orders'!F2:F36,A18,'Branch Orders'!H2:H36)</f>
+        <f>SUMIF('Branch Orders'!F2:F13,A18,'Branch Orders'!H2:H13)</f>
         <v/>
       </c>
       <c r="C18" s="12">
-        <f>COUNTIF('Branch Orders'!F2:F36,A18)</f>
+        <f>COUNTIF('Branch Orders'!F2:F13,A18)</f>
         <v/>
       </c>
     </row>
